--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125CECC5-E103-4F60-958F-32360BB073A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7AF34-AE08-43E5-A2E7-9A8192915AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12360" yWindow="195" windowWidth="16335" windowHeight="11490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -115,73 +115,82 @@
     <t>mrb-girls</t>
   </si>
   <si>
-    <t>KG_TEACHER</t>
-  </si>
-  <si>
     <t>BOYS_TEACHER لمعلمي البنين، أو GIRLS_TEACHER لمعلمات البنات.  -- KG_TEACHER</t>
   </si>
   <si>
-    <t>ندى عبدالله الموسى</t>
-  </si>
-  <si>
-    <t>جواهر عبدالله دخيل الفهيد</t>
-  </si>
-  <si>
-    <t>انفال عبدالله أحمد السلمان</t>
-  </si>
-  <si>
-    <t>اروى يوسف احمد الطيار</t>
-  </si>
-  <si>
-    <t>ساره عبدالله علي البدر</t>
-  </si>
-  <si>
-    <t>نوره سليمان صالح الخنيني</t>
-  </si>
-  <si>
-    <t>شروق يوسف عبدالله الذويخ</t>
-  </si>
-  <si>
-    <t>KF100000147</t>
-  </si>
-  <si>
-    <t>KF100000148</t>
-  </si>
-  <si>
-    <t>KF100000149</t>
-  </si>
-  <si>
-    <t>KF100000150</t>
-  </si>
-  <si>
-    <t>KF100000151</t>
-  </si>
-  <si>
-    <t>KF100000152</t>
-  </si>
-  <si>
-    <t>KF100000153</t>
-  </si>
-  <si>
-    <t>n.almosa@qz.org.sa</t>
-  </si>
-  <si>
-    <t>g.alfahid@qz.org.sa</t>
-  </si>
-  <si>
-    <t>an.alslman@qz.org.sa</t>
-  </si>
-  <si>
-    <t>a.alttayar@qz.org.sa</t>
-  </si>
-  <si>
-    <t>s.bader@qz.org.sa</t>
-  </si>
-  <si>
-    <t>n.alkhunini@qz.org.sa</t>
-  </si>
-  <si>
-    <t>sh.aldhuwaikh@qz.org.sa</t>
+    <t>عبدالله محمد الطيار</t>
+  </si>
+  <si>
+    <t>a-m-atyar@qz.org.sa</t>
+  </si>
+  <si>
+    <t>BOYS_TEACHER</t>
+  </si>
+  <si>
+    <t>Missing account from teacher assignment TEACHER_SCOPE preview</t>
+  </si>
+  <si>
+    <t>أحمد بن سعدون العبدالمنعم</t>
+  </si>
+  <si>
+    <t>a-s-alabdelmnem@qz.org.sa</t>
+  </si>
+  <si>
+    <t>بسام هلال البهلال</t>
+  </si>
+  <si>
+    <t>b-h-elbhlal@qz.org.sa</t>
+  </si>
+  <si>
+    <t>محمد فهد الحمين</t>
+  </si>
+  <si>
+    <t>m-f-elhmien@qz.org.sa</t>
+  </si>
+  <si>
+    <t>سهيل بن سعود الجديع</t>
+  </si>
+  <si>
+    <t>s-s-agedie@qz.org.sa</t>
+  </si>
+  <si>
+    <t>بدر إبراهيم عبدالله الرويشد</t>
+  </si>
+  <si>
+    <t>b-e-arweshid@qz.org.sa</t>
+  </si>
+  <si>
+    <t>خالد بن عبدالله الطريقي</t>
+  </si>
+  <si>
+    <t>kh-a-atriqi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>خالد بن محمد السحيمي</t>
+  </si>
+  <si>
+    <t>kh-m-asyhemi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>مؤيد فهد عبداللطيف الفهد</t>
+  </si>
+  <si>
+    <t>m-f-elfahd@qz.org.sa</t>
+  </si>
+  <si>
+    <t>ريان عبدالرحمن سليمان الطريقي</t>
+  </si>
+  <si>
+    <t>r-a-atriqi@qz.org.sa</t>
+  </si>
+  <si>
+    <t>طيف علي الدوسري</t>
+  </si>
+  <si>
+    <t>t.aldawsari@qz.org.sa</t>
+  </si>
+  <si>
+    <t>GIRLS_TEACHER</t>
   </si>
 </sst>
 </file>
@@ -201,20 +210,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Tajawal"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Google Sans"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -236,14 +246,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3F3F3"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -253,21 +263,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -281,11 +276,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,32 +303,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,17 +328,17 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <name val="Google Sans"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Tajawal"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <right style="medium">
           <color rgb="FFCCCCCC"/>
@@ -362,6 +363,17 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Google Sans"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -376,14 +388,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H12">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="الرقم الوظيفي"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="حالة الحساب"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ملاحظات"/>
   </tableColumns>
@@ -540,19 +552,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="24" style="7" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" thickBot="1">
+    <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,173 +591,263 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" thickBot="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" ht="24" customHeight="1">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="7">
+        <v>1118303070</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="24" customHeight="1">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1095275804</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1106628777</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1094841713</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1106437500</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1094337068</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="6">
-        <v>1102078480</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="5" t="s">
+      <c r="C8" s="8">
+        <v>1103409288</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="6">
-        <v>1099422246</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="B9" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="7">
-        <v>1109217438</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="C9" s="8">
+        <v>1100801008</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="7">
-        <v>1099014340</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="7">
-        <v>1061227870</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="C10" s="8">
+        <v>1092658119</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7">
-        <v>1015887209</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="7">
-        <v>1084087038</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>9</v>
+      <c r="C11" s="8">
+        <v>1119767794</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1105590366</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G8" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2:G12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
@@ -767,13 +870,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -784,7 +887,7 @@
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -795,7 +898,7 @@
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -806,7 +909,7 @@
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -817,7 +920,7 @@
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -828,7 +931,7 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -837,9 +940,9 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -850,7 +953,7 @@
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>26</v>
       </c>
     </row>

--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B7AF34-AE08-43E5-A2E7-9A8192915AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1450F882-C123-416C-807A-7775597DD9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7860" yWindow="45" windowWidth="20925" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -118,79 +118,25 @@
     <t>BOYS_TEACHER لمعلمي البنين، أو GIRLS_TEACHER لمعلمات البنات.  -- KG_TEACHER</t>
   </si>
   <si>
-    <t>عبدالله محمد الطيار</t>
-  </si>
-  <si>
-    <t>a-m-atyar@qz.org.sa</t>
-  </si>
-  <si>
-    <t>BOYS_TEACHER</t>
-  </si>
-  <si>
-    <t>Missing account from teacher assignment TEACHER_SCOPE preview</t>
-  </si>
-  <si>
-    <t>أحمد بن سعدون العبدالمنعم</t>
-  </si>
-  <si>
-    <t>a-s-alabdelmnem@qz.org.sa</t>
-  </si>
-  <si>
-    <t>بسام هلال البهلال</t>
-  </si>
-  <si>
-    <t>b-h-elbhlal@qz.org.sa</t>
-  </si>
-  <si>
-    <t>محمد فهد الحمين</t>
-  </si>
-  <si>
-    <t>m-f-elhmien@qz.org.sa</t>
-  </si>
-  <si>
-    <t>سهيل بن سعود الجديع</t>
-  </si>
-  <si>
-    <t>s-s-agedie@qz.org.sa</t>
-  </si>
-  <si>
-    <t>بدر إبراهيم عبدالله الرويشد</t>
-  </si>
-  <si>
-    <t>b-e-arweshid@qz.org.sa</t>
-  </si>
-  <si>
-    <t>خالد بن عبدالله الطريقي</t>
-  </si>
-  <si>
-    <t>kh-a-atriqi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>خالد بن محمد السحيمي</t>
-  </si>
-  <si>
-    <t>kh-m-asyhemi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>مؤيد فهد عبداللطيف الفهد</t>
-  </si>
-  <si>
-    <t>m-f-elfahd@qz.org.sa</t>
-  </si>
-  <si>
-    <t>ريان عبدالرحمن سليمان الطريقي</t>
-  </si>
-  <si>
-    <t>r-a-atriqi@qz.org.sa</t>
-  </si>
-  <si>
-    <t>طيف علي الدوسري</t>
-  </si>
-  <si>
-    <t>t.aldawsari@qz.org.sa</t>
-  </si>
-  <si>
     <t>GIRLS_TEACHER</t>
+  </si>
+  <si>
+    <t>وعد علي الطوالة</t>
+  </si>
+  <si>
+    <t>w-a-atwala@qz.org.sa</t>
+  </si>
+  <si>
+    <t>نوره ربيعة الربيعة</t>
+  </si>
+  <si>
+    <t>n-r-arbya@qz.org.sa</t>
+  </si>
+  <si>
+    <t>ريم جوير الفراج</t>
+  </si>
+  <si>
+    <t>r-g-alfraj@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -217,17 +163,17 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Tajawal"/>
+      <sz val="18"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,20 +190,8 @@
         <fgColor rgb="FF0F766E"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -273,21 +207,6 @@
       </top>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -315,36 +234,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Tajawal"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -374,6 +270,25 @@
         </left>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Tajawal"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -388,14 +303,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H4">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="كلمة المرور المؤقتة" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="الرقم الوظيفي"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="معرّف المدرسة" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{EEC87794-B495-480E-A000-1DA2F577E634}" name="الدور" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="حالة الحساب"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ملاحظات"/>
   </tableColumns>
@@ -552,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
@@ -565,7 +480,7 @@
     <col min="8" max="8" width="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
+    <row r="1" spans="1:8" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,270 +506,80 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" ht="23.25">
+      <c r="A2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>1111478259</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
         <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1118303070</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="23.25">
+      <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" t="s">
+      <c r="B3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1095275804</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>1108811546</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="23.25">
+      <c r="A4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1106628777</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
+      <c r="C4">
+        <v>1110636832</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1094841713</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1106437500</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1094337068</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1103409288</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1100801008</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1092658119</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1119767794</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1105590366</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2:G4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{908124A5-F561-4B08-8329-51715E94F5EE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1450F882-C123-416C-807A-7775597DD9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7384299-0240-46A6-ADD1-FC166997F696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="45" windowWidth="20925" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="7200" windowWidth="14100" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -118,32 +118,26 @@
     <t>BOYS_TEACHER لمعلمي البنين، أو GIRLS_TEACHER لمعلمات البنات.  -- KG_TEACHER</t>
   </si>
   <si>
-    <t>GIRLS_TEACHER</t>
-  </si>
-  <si>
-    <t>وعد علي الطوالة</t>
-  </si>
-  <si>
-    <t>w-a-atwala@qz.org.sa</t>
-  </si>
-  <si>
-    <t>نوره ربيعة الربيعة</t>
-  </si>
-  <si>
-    <t>n-r-arbya@qz.org.sa</t>
-  </si>
-  <si>
-    <t>ريم جوير الفراج</t>
-  </si>
-  <si>
-    <t>r-g-alfraj@qz.org.sa</t>
+    <t>الهنوف سليمان عبدالله الفرهود</t>
+  </si>
+  <si>
+    <t>a-s-alfrhood@qz.org.sa</t>
+  </si>
+  <si>
+    <t>KG_TEACHER</t>
+  </si>
+  <si>
+    <t>r-a-atyar@qz.org.sa</t>
+  </si>
+  <si>
+    <t>رهام عبدالله محمد الطيار</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -169,6 +163,11 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -214,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +235,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H3">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
@@ -508,78 +508,55 @@
     </row>
     <row r="2" spans="1:8" ht="23.25">
       <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="9">
+        <v>1125262517</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2">
-        <v>1111478259</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="23.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3">
-        <v>1108811546</v>
+      <c r="C3" s="9">
+        <v>1118302858</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="23.25">
-      <c r="A4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
-        <v>1110636832</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G4" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2:G3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{908124A5-F561-4B08-8329-51715E94F5EE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7384299-0240-46A6-ADD1-FC166997F696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272B9F45-10F9-4108-88FB-3D0F5EFF6C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="7200" windowWidth="14100" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="2370" windowWidth="15645" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -118,26 +118,23 @@
     <t>BOYS_TEACHER لمعلمي البنين، أو GIRLS_TEACHER لمعلمات البنات.  -- KG_TEACHER</t>
   </si>
   <si>
-    <t>الهنوف سليمان عبدالله الفرهود</t>
-  </si>
-  <si>
-    <t>a-s-alfrhood@qz.org.sa</t>
-  </si>
-  <si>
-    <t>KG_TEACHER</t>
-  </si>
-  <si>
-    <t>r-a-atyar@qz.org.sa</t>
-  </si>
-  <si>
-    <t>رهام عبدالله محمد الطيار</t>
+    <t>حامد السيد السيد نافع</t>
+  </si>
+  <si>
+    <t>hameed-s@qz.org.sa</t>
+  </si>
+  <si>
+    <t>KF100000030</t>
+  </si>
+  <si>
+    <t>BOYS_TEACHER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -157,19 +154,8 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="18"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Tajawal"/>
     </font>
   </fonts>
   <fills count="4">
@@ -213,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,8 +220,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,7 +287,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H2">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
@@ -467,17 +451,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15">
@@ -506,50 +490,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="23.25">
+    <row r="2" spans="1:8" ht="16.5">
       <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="9">
-        <v>1125262517</v>
+      <c r="C2" s="7">
+        <v>2550897843</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="9">
-        <v>1118302858</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
